--- a/growth_rate/1_bilogito.xlsx
+++ b/growth_rate/1_bilogito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lenin/Documents/Programacion/COLMEX/data-for-social-science/growth_rate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DB2DCB-44F1-0144-B64A-70AAEA241735}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B152DB6-33B0-C948-9AED-2894818E1DE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="45260" windowHeight="20860" activeTab="3" xr2:uid="{6605802F-6F3A-415B-9EF1-3DCDC16990EE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="45260" windowHeight="20860" activeTab="2" xr2:uid="{6605802F-6F3A-415B-9EF1-3DCDC16990EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bilogito" sheetId="13" r:id="rId1"/>
@@ -41948,412 +41948,157 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1">
-        <v>2020</v>
-      </c>
-      <c r="B32" s="18">
-        <v>1.9854682279135301</v>
-      </c>
+      <c r="B32" s="18"/>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="1">
-        <v>2021</v>
-      </c>
-      <c r="B33" s="18">
-        <v>1.9425844596111299</v>
-      </c>
+    <row r="33" spans="2:2">
+      <c r="B33" s="18"/>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="1">
-        <v>2022</v>
-      </c>
-      <c r="B34" s="18">
-        <v>1.9067111742038001</v>
-      </c>
+    <row r="34" spans="2:2">
+      <c r="B34" s="18"/>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="1">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="18">
-        <v>1.8812483225724901</v>
-      </c>
+    <row r="35" spans="2:2">
+      <c r="B35" s="18"/>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="1">
-        <v>2024</v>
-      </c>
-      <c r="B36" s="18">
-        <v>1.85878707441433</v>
-      </c>
+    <row r="36" spans="2:2">
+      <c r="B36" s="18"/>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="1">
-        <v>2025</v>
-      </c>
-      <c r="B37" s="18">
-        <v>1.83348052274602</v>
-      </c>
+    <row r="37" spans="2:2">
+      <c r="B37" s="18"/>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="1">
-        <v>2026</v>
-      </c>
-      <c r="B38" s="18">
-        <v>1.8064149920633501</v>
-      </c>
+    <row r="38" spans="2:2">
+      <c r="B38" s="18"/>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="1">
-        <v>2027</v>
-      </c>
-      <c r="B39" s="18">
-        <v>1.7814243459318699</v>
-      </c>
+    <row r="39" spans="2:2">
+      <c r="B39" s="18"/>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="1">
-        <v>2028</v>
-      </c>
-      <c r="B40" s="18">
-        <v>1.75990594737036</v>
-      </c>
+    <row r="40" spans="2:2">
+      <c r="B40" s="18"/>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="1">
-        <v>2029</v>
-      </c>
-      <c r="B41" s="18">
-        <v>1.74054179612982</v>
-      </c>
+    <row r="41" spans="2:2">
+      <c r="B41" s="18"/>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1">
-        <v>2030</v>
-      </c>
-      <c r="B42" s="18">
-        <v>1.7218535085939699</v>
-      </c>
+    <row r="42" spans="2:2">
+      <c r="B42" s="18"/>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="1">
-        <v>2031</v>
-      </c>
-      <c r="B43" s="18">
-        <v>1.70372667256615</v>
-      </c>
+    <row r="43" spans="2:2">
+      <c r="B43" s="18"/>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="1">
-        <v>2032</v>
-      </c>
-      <c r="B44" s="18">
-        <v>1.6868431680479901</v>
-      </c>
+    <row r="44" spans="2:2">
+      <c r="B44" s="18"/>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="1">
-        <v>2033</v>
-      </c>
-      <c r="B45" s="18">
-        <v>1.6715592400539501</v>
-      </c>
+    <row r="45" spans="2:2">
+      <c r="B45" s="18"/>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="1">
-        <v>2034</v>
-      </c>
-      <c r="B46" s="18">
-        <v>1.65763793918062</v>
-      </c>
+    <row r="46" spans="2:2">
+      <c r="B46" s="18"/>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="1">
-        <v>2035</v>
-      </c>
-      <c r="B47" s="18">
-        <v>1.64470172828529</v>
-      </c>
+    <row r="47" spans="2:2">
+      <c r="B47" s="18"/>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="1">
-        <v>2036</v>
-      </c>
-      <c r="B48" s="18">
-        <v>1.6326118448070299</v>
-      </c>
+    <row r="48" spans="2:2">
+      <c r="B48" s="18"/>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="1">
-        <v>2037</v>
-      </c>
-      <c r="B49" s="18">
-        <v>1.62142939678719</v>
-      </c>
+    <row r="49" spans="2:2">
+      <c r="B49" s="18"/>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="1">
-        <v>2038</v>
-      </c>
-      <c r="B50" s="18">
-        <v>1.6111947206019801</v>
-      </c>
+    <row r="50" spans="2:2">
+      <c r="B50" s="18"/>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="1">
-        <v>2039</v>
-      </c>
-      <c r="B51" s="18">
-        <v>1.6018343454765001</v>
-      </c>
+    <row r="51" spans="2:2">
+      <c r="B51" s="18"/>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="1">
-        <v>2040</v>
-      </c>
-      <c r="B52" s="18">
-        <v>1.5932287611918301</v>
-      </c>
+    <row r="52" spans="2:2">
+      <c r="B52" s="18"/>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="1">
-        <v>2041</v>
-      </c>
-      <c r="B53" s="18">
-        <v>1.5852966794696499</v>
-      </c>
+    <row r="53" spans="2:2">
+      <c r="B53" s="18"/>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1">
-        <v>2042</v>
-      </c>
-      <c r="B54" s="18">
-        <v>1.57800376383576</v>
-      </c>
+    <row r="54" spans="2:2">
+      <c r="B54" s="18"/>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="1">
-        <v>2043</v>
-      </c>
-      <c r="B55" s="18">
-        <v>1.5713231564573</v>
-      </c>
+    <row r="55" spans="2:2">
+      <c r="B55" s="18"/>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="1">
-        <v>2044</v>
-      </c>
-      <c r="B56" s="18">
-        <v>1.56521044455324</v>
-      </c>
+    <row r="56" spans="2:2">
+      <c r="B56" s="18"/>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="1">
-        <v>2045</v>
-      </c>
-      <c r="B57" s="18">
-        <v>1.55961121460731</v>
-      </c>
+    <row r="57" spans="2:2">
+      <c r="B57" s="18"/>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="1">
-        <v>2046</v>
-      </c>
-      <c r="B58" s="18">
-        <v>1.5544779553915899</v>
-      </c>
+    <row r="58" spans="2:2">
+      <c r="B58" s="18"/>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="1">
-        <v>2047</v>
-      </c>
-      <c r="B59" s="18">
-        <v>1.5497748406026599</v>
-      </c>
+    <row r="59" spans="2:2">
+      <c r="B59" s="18"/>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="1">
-        <v>2048</v>
-      </c>
-      <c r="B60" s="18">
-        <v>1.54547131147975</v>
-      </c>
+    <row r="60" spans="2:2">
+      <c r="B60" s="18"/>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="1">
-        <v>2049</v>
-      </c>
-      <c r="B61" s="18">
-        <v>1.5415361269558301</v>
-      </c>
+    <row r="61" spans="2:2">
+      <c r="B61" s="18"/>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="1">
-        <v>2050</v>
-      </c>
-      <c r="B62" s="18">
-        <v>1.53793746799444</v>
-      </c>
+    <row r="62" spans="2:2">
+      <c r="B62" s="18"/>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="1">
-        <v>2051</v>
-      </c>
-      <c r="B63" s="18">
-        <v>1.5346459392920699</v>
-      </c>
+    <row r="63" spans="2:2">
+      <c r="B63" s="18"/>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="1">
-        <v>2052</v>
-      </c>
-      <c r="B64" s="18">
-        <v>1.53163593542217</v>
-      </c>
+    <row r="64" spans="2:2">
+      <c r="B64" s="18"/>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="1">
-        <v>2053</v>
-      </c>
-      <c r="B65" s="18">
-        <v>1.5288846544613901</v>
-      </c>
+    <row r="65" spans="2:2">
+      <c r="B65" s="18"/>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="1">
-        <v>2054</v>
-      </c>
-      <c r="B66" s="18">
-        <v>1.5263707391211401</v>
-      </c>
+    <row r="66" spans="2:2">
+      <c r="B66" s="18"/>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="1">
-        <v>2055</v>
-      </c>
-      <c r="B67" s="18">
-        <v>1.5240739475696901</v>
-      </c>
+    <row r="67" spans="2:2">
+      <c r="B67" s="18"/>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="1">
-        <v>2056</v>
-      </c>
-      <c r="B68" s="18">
-        <v>1.5219755575899201</v>
-      </c>
+    <row r="68" spans="2:2">
+      <c r="B68" s="18"/>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="1">
-        <v>2057</v>
-      </c>
-      <c r="B69" s="18">
-        <v>1.5200586248583301</v>
-      </c>
+    <row r="69" spans="2:2">
+      <c r="B69" s="18"/>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="1">
-        <v>2058</v>
-      </c>
-      <c r="B70" s="18">
-        <v>1.5183077921418699</v>
-      </c>
+    <row r="70" spans="2:2">
+      <c r="B70" s="18"/>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="1">
-        <v>2059</v>
-      </c>
-      <c r="B71" s="18">
-        <v>1.51670894697882</v>
-      </c>
+    <row r="71" spans="2:2">
+      <c r="B71" s="18"/>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="1">
-        <v>2060</v>
-      </c>
-      <c r="B72" s="18">
-        <v>1.5152490394557601</v>
-      </c>
+    <row r="72" spans="2:2">
+      <c r="B72" s="18"/>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="1">
-        <v>2061</v>
-      </c>
-      <c r="B73" s="18">
-        <v>1.51391606808512</v>
-      </c>
+    <row r="73" spans="2:2">
+      <c r="B73" s="18"/>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="1">
-        <v>2062</v>
-      </c>
-      <c r="B74" s="18">
-        <v>1.51269907669746</v>
-      </c>
+    <row r="74" spans="2:2">
+      <c r="B74" s="18"/>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1">
-        <v>2063</v>
-      </c>
-      <c r="B75" s="18">
-        <v>1.5115880763523799</v>
-      </c>
+    <row r="75" spans="2:2">
+      <c r="B75" s="18"/>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="1">
-        <v>2064</v>
-      </c>
-      <c r="B76" s="18">
-        <v>1.51057392850022</v>
-      </c>
+    <row r="76" spans="2:2">
+      <c r="B76" s="18"/>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="1">
-        <v>2065</v>
-      </c>
-      <c r="B77" s="18">
-        <v>1.50964825239119</v>
-      </c>
+    <row r="77" spans="2:2">
+      <c r="B77" s="18"/>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="1">
-        <v>2066</v>
-      </c>
-      <c r="B78" s="18">
-        <v>1.5088033704674799</v>
-      </c>
+    <row r="78" spans="2:2">
+      <c r="B78" s="18"/>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="1">
-        <v>2067</v>
-      </c>
-      <c r="B79" s="18">
-        <v>1.5080322660347301</v>
-      </c>
+    <row r="79" spans="2:2">
+      <c r="B79" s="18"/>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="1">
-        <v>2068</v>
-      </c>
-      <c r="B80" s="18">
-        <v>1.5073285324516501</v>
-      </c>
+    <row r="80" spans="2:2">
+      <c r="B80" s="18"/>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="1">
-        <v>2069</v>
-      </c>
-      <c r="B81" s="18">
-        <v>1.50668631601548</v>
-      </c>
+    <row r="81" spans="2:2">
+      <c r="B81" s="18"/>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="1">
-        <v>2070</v>
-      </c>
-      <c r="B82" s="18">
-        <v>1.5061002641004799</v>
-      </c>
+    <row r="82" spans="2:2">
+      <c r="B82" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
